--- a/outputs/tables/tabla_comparacion_modelos_bayesiana.xlsx
+++ b/outputs/tables/tabla_comparacion_modelos_bayesiana.xlsx
@@ -14,45 +14,66 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
   <si>
     <t>Modelo</t>
   </si>
   <si>
-    <t>WAIC</t>
-  </si>
-  <si>
-    <t>LOO-CV</t>
-  </si>
-  <si>
-    <t>p_WAIC (Parámetros Efectivos)</t>
-  </si>
-  <si>
-    <t>Estado / Decisión</t>
-  </si>
-  <si>
-    <t>Poisson Bayesiano Jerárquico</t>
-  </si>
-  <si>
-    <t>Zero-Inflated Poisson (ZIP) Bayesiano</t>
-  </si>
-  <si>
-    <t>Binomial Negativa Bayesiano Jerárquico (Actual)</t>
-  </si>
-  <si>
-    <t>BYM2 Binomial Negativo (Ajuste Alternativo)</t>
-  </si>
-  <si>
-    <t>Descartado (Omite sobredispersión extrema)</t>
-  </si>
-  <si>
-    <t>Descartado (Subestima la cola de conteos altos)</t>
-  </si>
-  <si>
-    <t>Seleccionado (Óptimo ajuste de sobredispersión)</t>
-  </si>
-  <si>
-    <t>Alternativa Aceptada (Estructura espacial optimizada)</t>
+    <t>rank</t>
+  </si>
+  <si>
+    <t>elpd_loo</t>
+  </si>
+  <si>
+    <t>p_loo</t>
+  </si>
+  <si>
+    <t>elpd_diff</t>
+  </si>
+  <si>
+    <t>weight</t>
+  </si>
+  <si>
+    <t>se</t>
+  </si>
+  <si>
+    <t>dse</t>
+  </si>
+  <si>
+    <t>warning</t>
+  </si>
+  <si>
+    <t>scale</t>
+  </si>
+  <si>
+    <t>Diagnóstico Pareto-k</t>
+  </si>
+  <si>
+    <t>BYM2 Binomial Negativo (Prior PC)</t>
+  </si>
+  <si>
+    <t>Binomial Negativa (ICAR + No Estructurado)</t>
+  </si>
+  <si>
+    <t>Binomial Negativa (ICAR)</t>
+  </si>
+  <si>
+    <t>Poisson Jerárquico</t>
+  </si>
+  <si>
+    <t>log</t>
+  </si>
+  <si>
+    <t>k&lt;0.5: 290, 0.5&lt;=k&lt;=0.7: 139, k&gt;0.7: 59</t>
+  </si>
+  <si>
+    <t>k&lt;0.5: 291, 0.5&lt;=k&lt;=0.7: 151, k&gt;0.7: 46</t>
+  </si>
+  <si>
+    <t>k&lt;0.5: 290, 0.5&lt;=k&lt;=0.7: 154, k&gt;0.7: 44</t>
+  </si>
+  <si>
+    <t>k&lt;0.5: 194, 0.5&lt;=k&lt;=0.7: 181, k&gt;0.7: 113</t>
   </si>
 </sst>
 </file>
@@ -410,10 +431,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -429,73 +450,163 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B2">
-        <v>8223.634420031594</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>8410.313494145623</v>
+        <v>-1321.272312148847</v>
       </c>
       <c r="D2">
-        <v>235.4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
+        <v>167.762288234436</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0.5322113357589838</v>
+      </c>
+      <c r="G2">
+        <v>26.73173442791879</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B3">
-        <v>6167.725815023696</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>6469.471918573557</v>
+        <v>-1321.369357359431</v>
       </c>
       <c r="D3">
-        <v>252.1</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
+        <v>168.6391454761633</v>
+      </c>
+      <c r="E3">
+        <v>0.09704521058482474</v>
+      </c>
+      <c r="F3">
+        <v>0.3852619949837823</v>
+      </c>
+      <c r="G3">
+        <v>26.81562314243196</v>
+      </c>
+      <c r="H3">
+        <v>1.183570288136394</v>
+      </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K3" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B4">
-        <v>4111.817210015797</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>4312.981279049038</v>
+        <v>-1323.985452771909</v>
       </c>
       <c r="D4">
-        <v>143.8</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
+        <v>164.5193368863249</v>
+      </c>
+      <c r="E4">
+        <v>2.713140623062484</v>
+      </c>
+      <c r="F4">
+        <v>2.070012997817949E-16</v>
+      </c>
+      <c r="G4">
+        <v>27.06417381493658</v>
+      </c>
+      <c r="H4">
+        <v>2.381441370986644</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K4" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B5">
-        <v>4095.369941175734</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>4287.103391374743</v>
+        <v>-1434.350933958609</v>
       </c>
       <c r="D5">
-        <v>124.5</v>
-      </c>
-      <c r="E5" t="s">
-        <v>12</v>
+        <v>360.2189361417338</v>
+      </c>
+      <c r="E5">
+        <v>113.0786218097623</v>
+      </c>
+      <c r="F5">
+        <v>0.08252666925723359</v>
+      </c>
+      <c r="G5">
+        <v>43.59712729834377</v>
+      </c>
+      <c r="H5">
+        <v>24.43037641295739</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tables/tabla_comparacion_modelos_bayesiana.xlsx
+++ b/outputs/tables/tabla_comparacion_modelos_bayesiana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
   <si>
     <t>Modelo</t>
   </si>
@@ -46,15 +46,39 @@
     <t>scale</t>
   </si>
   <si>
-    <t>Diagnóstico Pareto-k</t>
-  </si>
-  <si>
-    <t>BYM2 Binomial Negativo (Prior PC)</t>
+    <t>ELBO_Final</t>
+  </si>
+  <si>
+    <t>Iteraciones_ADVI</t>
+  </si>
+  <si>
+    <t>Convergio</t>
+  </si>
+  <si>
+    <t>k &lt; 0.5</t>
+  </si>
+  <si>
+    <t>0.5 &lt;= k &lt;= 0.7</t>
+  </si>
+  <si>
+    <t>k &gt; 0.7</t>
+  </si>
+  <si>
+    <t>Advertencia_Pareto_k</t>
+  </si>
+  <si>
+    <t>elpd_waic</t>
+  </si>
+  <si>
+    <t>p_waic</t>
   </si>
   <si>
     <t>Binomial Negativa (ICAR + No Estructurado)</t>
   </si>
   <si>
+    <t>BYM2 Binomial Negativo (Prior Beta(0.5, 0.5))</t>
+  </si>
+  <si>
     <t>Binomial Negativa (ICAR)</t>
   </si>
   <si>
@@ -64,16 +88,7 @@
     <t>log</t>
   </si>
   <si>
-    <t>k&lt;0.5: 290, 0.5&lt;=k&lt;=0.7: 139, k&gt;0.7: 59</t>
-  </si>
-  <si>
-    <t>k&lt;0.5: 291, 0.5&lt;=k&lt;=0.7: 151, k&gt;0.7: 46</t>
-  </si>
-  <si>
-    <t>k&lt;0.5: 290, 0.5&lt;=k&lt;=0.7: 154, k&gt;0.7: 44</t>
-  </si>
-  <si>
-    <t>k&lt;0.5: 194, 0.5&lt;=k&lt;=0.7: 181, k&gt;0.7: 113</t>
+    <t>Advertencia: observaciones con k&gt;0.7 presentes</t>
   </si>
 </sst>
 </file>
@@ -431,10 +446,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:19">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -468,28 +483,52 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>-1321.272312148847</v>
+        <v>-1504.985609926481</v>
       </c>
       <c r="D2">
-        <v>167.762288234436</v>
+        <v>247.8190932562088</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.5322113357589838</v>
+        <v>0.8744672541871844</v>
       </c>
       <c r="G2">
-        <v>26.73173442791879</v>
+        <v>30.49537945123489</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -498,115 +537,211 @@
         <v>1</v>
       </c>
       <c r="J2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K2" t="s">
-        <v>16</v>
+        <v>23</v>
+      </c>
+      <c r="K2">
+        <v>-3336.360347741149</v>
+      </c>
+      <c r="L2">
+        <v>40000</v>
+      </c>
+      <c r="M2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>213</v>
+      </c>
+      <c r="O2">
+        <v>131</v>
+      </c>
+      <c r="P2">
+        <v>144</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R2">
+        <v>-1436.797811011564</v>
+      </c>
+      <c r="S2">
+        <v>179.6312943412921</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3">
-        <v>-1321.369357359431</v>
+        <v>-1537.056294417802</v>
       </c>
       <c r="D3">
-        <v>168.6391454761633</v>
+        <v>231.316994224389</v>
       </c>
       <c r="E3">
-        <v>0.09704521058482474</v>
+        <v>32.07068449132084</v>
       </c>
       <c r="F3">
-        <v>0.3852619949837823</v>
+        <v>4.636476419134635E-11</v>
       </c>
       <c r="G3">
-        <v>26.81562314243196</v>
+        <v>30.86485530288633</v>
       </c>
       <c r="H3">
-        <v>1.183570288136394</v>
+        <v>2.773949600319149</v>
       </c>
       <c r="I3" t="b">
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>15</v>
-      </c>
-      <c r="K3" t="s">
-        <v>17</v>
+        <v>23</v>
+      </c>
+      <c r="K3">
+        <v>-3359.574986593439</v>
+      </c>
+      <c r="L3">
+        <v>40000</v>
+      </c>
+      <c r="M3" t="b">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>242</v>
+      </c>
+      <c r="O3">
+        <v>100</v>
+      </c>
+      <c r="P3">
+        <v>146</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>24</v>
+      </c>
+      <c r="R3">
+        <v>-1473.724258527367</v>
+      </c>
+      <c r="S3">
+        <v>167.9849583339543</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B4">
         <v>2</v>
       </c>
       <c r="C4">
-        <v>-1323.985452771909</v>
+        <v>-1560.587226657748</v>
       </c>
       <c r="D4">
-        <v>164.5193368863249</v>
+        <v>11.01715765462177</v>
       </c>
       <c r="E4">
-        <v>2.713140623062484</v>
+        <v>55.60161673126709</v>
       </c>
       <c r="F4">
-        <v>2.070012997817949E-16</v>
+        <v>0.1255327457033273</v>
       </c>
       <c r="G4">
-        <v>27.06417381493658</v>
+        <v>26.90273470931896</v>
       </c>
       <c r="H4">
-        <v>2.381441370986644</v>
+        <v>12.05761787256209</v>
       </c>
       <c r="I4" t="b">
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K4" t="s">
-        <v>18</v>
+        <v>23</v>
+      </c>
+      <c r="K4">
+        <v>-1662.807344541952</v>
+      </c>
+      <c r="L4">
+        <v>40000</v>
+      </c>
+      <c r="M4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>355</v>
+      </c>
+      <c r="O4">
+        <v>97</v>
+      </c>
+      <c r="P4">
+        <v>36</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>24</v>
+      </c>
+      <c r="R4">
+        <v>-1560.320734689263</v>
+      </c>
+      <c r="S4">
+        <v>10.75066568613641</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B5">
         <v>3</v>
       </c>
       <c r="C5">
-        <v>-1434.350933958609</v>
+        <v>-1951.152173705433</v>
       </c>
       <c r="D5">
-        <v>360.2189361417338</v>
+        <v>825.3113340132597</v>
       </c>
       <c r="E5">
-        <v>113.0786218097623</v>
+        <v>446.1665637789517</v>
       </c>
       <c r="F5">
-        <v>0.08252666925723359</v>
+        <v>6.312363483505758E-11</v>
       </c>
       <c r="G5">
-        <v>43.59712729834377</v>
+        <v>65.01894475091952</v>
       </c>
       <c r="H5">
-        <v>24.43037641295739</v>
+        <v>45.26142305921647</v>
       </c>
       <c r="I5" t="b">
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>15</v>
-      </c>
-      <c r="K5" t="s">
-        <v>19</v>
+        <v>23</v>
+      </c>
+      <c r="K5">
+        <v>-1651.283804041921</v>
+      </c>
+      <c r="L5">
+        <v>40000</v>
+      </c>
+      <c r="M5" t="b">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>61</v>
+      </c>
+      <c r="O5">
+        <v>116</v>
+      </c>
+      <c r="P5">
+        <v>311</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>24</v>
+      </c>
+      <c r="R5">
+        <v>-1728.337383867849</v>
+      </c>
+      <c r="S5">
+        <v>602.4965441756756</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tables/tabla_comparacion_modelos_bayesiana.xlsx
+++ b/outputs/tables/tabla_comparacion_modelos_bayesiana.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="28">
   <si>
     <t>Modelo</t>
   </si>
@@ -49,6 +49,12 @@
     <t>ELBO_Final</t>
   </si>
   <si>
+    <t>Variacion_ELBO_5k_Pct</t>
+  </si>
+  <si>
+    <t>Criterio_Convergencia</t>
+  </si>
+  <si>
     <t>Iteraciones_ADVI</t>
   </si>
   <si>
@@ -73,19 +79,22 @@
     <t>p_waic</t>
   </si>
   <si>
+    <t>Binomial Negativa (ICAR)</t>
+  </si>
+  <si>
     <t>Binomial Negativa (ICAR + No Estructurado)</t>
   </si>
   <si>
     <t>BYM2 Binomial Negativo (Prior Beta(0.5, 0.5))</t>
   </si>
   <si>
-    <t>Binomial Negativa (ICAR)</t>
-  </si>
-  <si>
     <t>Poisson Jerárquico</t>
   </si>
   <si>
     <t>log</t>
+  </si>
+  <si>
+    <t>Var 5k &lt; 0.1%</t>
   </si>
   <si>
     <t>Advertencia: observaciones con k&gt;0.7 presentes</t>
@@ -446,10 +455,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S5"/>
+  <dimension ref="A1:U5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:21">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -507,28 +516,34 @@
       <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:21">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>-1504.985609926481</v>
+        <v>-1233.7458212532</v>
       </c>
       <c r="D2">
-        <v>247.8190932562088</v>
+        <v>117.6564035434187</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.8744672541871844</v>
+        <v>0.9901962602956861</v>
       </c>
       <c r="G2">
-        <v>30.49537945123489</v>
+        <v>26.7589567450958</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -537,211 +552,235 @@
         <v>1</v>
       </c>
       <c r="J2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2">
+        <v>-1463.565465992249</v>
+      </c>
+      <c r="L2">
+        <v>0.02392804933448085</v>
+      </c>
+      <c r="M2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2">
+        <v>50000</v>
+      </c>
+      <c r="O2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P2">
+        <v>371</v>
+      </c>
+      <c r="Q2">
+        <v>90</v>
+      </c>
+      <c r="R2">
+        <v>27</v>
+      </c>
+      <c r="S2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T2">
+        <v>-1219.559352321657</v>
+      </c>
+      <c r="U2">
+        <v>103.4699346118752</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>-1241.64798860666</v>
+      </c>
+      <c r="D3">
+        <v>126.0879422282337</v>
+      </c>
+      <c r="E3">
+        <v>7.902167353459357</v>
+      </c>
+      <c r="F3">
+        <v>0.00980373970429772</v>
+      </c>
+      <c r="G3">
+        <v>27.91618225178142</v>
+      </c>
+      <c r="H3">
+        <v>4.183752401269722</v>
+      </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3">
+        <v>-1480.205303364144</v>
+      </c>
+      <c r="L3">
+        <v>0.007568522033483955</v>
+      </c>
+      <c r="M3" t="s">
+        <v>26</v>
+      </c>
+      <c r="N3">
+        <v>50000</v>
+      </c>
+      <c r="O3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P3">
+        <v>355</v>
+      </c>
+      <c r="Q3">
+        <v>95</v>
+      </c>
+      <c r="R3">
+        <v>38</v>
+      </c>
+      <c r="S3" t="s">
+        <v>27</v>
+      </c>
+      <c r="T3">
+        <v>-1225.9192207671</v>
+      </c>
+      <c r="U3">
+        <v>110.3591743886742</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21">
+      <c r="A4" t="s">
         <v>23</v>
-      </c>
-      <c r="K2">
-        <v>-3336.360347741149</v>
-      </c>
-      <c r="L2">
-        <v>40000</v>
-      </c>
-      <c r="M2" t="b">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>213</v>
-      </c>
-      <c r="O2">
-        <v>131</v>
-      </c>
-      <c r="P2">
-        <v>144</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R2">
-        <v>-1436.797811011564</v>
-      </c>
-      <c r="S2">
-        <v>179.6312943412921</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19">
-      <c r="A3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>-1537.056294417802</v>
-      </c>
-      <c r="D3">
-        <v>231.316994224389</v>
-      </c>
-      <c r="E3">
-        <v>32.07068449132084</v>
-      </c>
-      <c r="F3">
-        <v>4.636476419134635E-11</v>
-      </c>
-      <c r="G3">
-        <v>30.86485530288633</v>
-      </c>
-      <c r="H3">
-        <v>2.773949600319149</v>
-      </c>
-      <c r="I3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J3" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3">
-        <v>-3359.574986593439</v>
-      </c>
-      <c r="L3">
-        <v>40000</v>
-      </c>
-      <c r="M3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>242</v>
-      </c>
-      <c r="O3">
-        <v>100</v>
-      </c>
-      <c r="P3">
-        <v>146</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>24</v>
-      </c>
-      <c r="R3">
-        <v>-1473.724258527367</v>
-      </c>
-      <c r="S3">
-        <v>167.9849583339543</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19">
-      <c r="A4" t="s">
-        <v>21</v>
       </c>
       <c r="B4">
         <v>2</v>
       </c>
       <c r="C4">
-        <v>-1560.587226657748</v>
+        <v>-1242.920149367842</v>
       </c>
       <c r="D4">
-        <v>11.01715765462177</v>
+        <v>127.3816142985363</v>
       </c>
       <c r="E4">
-        <v>55.60161673126709</v>
+        <v>9.174328114641327</v>
       </c>
       <c r="F4">
-        <v>0.1255327457033273</v>
+        <v>5.265694625791205E-14</v>
       </c>
       <c r="G4">
-        <v>26.90273470931896</v>
+        <v>28.02564984422117</v>
       </c>
       <c r="H4">
-        <v>12.05761787256209</v>
+        <v>4.352485765680648</v>
       </c>
       <c r="I4" t="b">
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K4">
-        <v>-1662.807344541952</v>
+        <v>-1479.389391621586</v>
       </c>
       <c r="L4">
-        <v>40000</v>
-      </c>
-      <c r="M4" t="b">
-        <v>0</v>
+        <v>0.005227421651050392</v>
+      </c>
+      <c r="M4" t="s">
+        <v>26</v>
       </c>
       <c r="N4">
-        <v>355</v>
-      </c>
-      <c r="O4">
-        <v>97</v>
+        <v>50000</v>
+      </c>
+      <c r="O4" t="b">
+        <v>1</v>
       </c>
       <c r="P4">
-        <v>36</v>
-      </c>
-      <c r="Q4" t="s">
+        <v>357</v>
+      </c>
+      <c r="Q4">
+        <v>96</v>
+      </c>
+      <c r="R4">
+        <v>35</v>
+      </c>
+      <c r="S4" t="s">
+        <v>27</v>
+      </c>
+      <c r="T4">
+        <v>-1226.453352676701</v>
+      </c>
+      <c r="U4">
+        <v>110.9148176073954</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21">
+      <c r="A5" t="s">
         <v>24</v>
-      </c>
-      <c r="R4">
-        <v>-1560.320734689263</v>
-      </c>
-      <c r="S4">
-        <v>10.75066568613641</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19">
-      <c r="A5" t="s">
-        <v>22</v>
       </c>
       <c r="B5">
         <v>3</v>
       </c>
       <c r="C5">
-        <v>-1951.152173705433</v>
+        <v>-1369.220687728424</v>
       </c>
       <c r="D5">
-        <v>825.3113340132597</v>
+        <v>302.1917474902152</v>
       </c>
       <c r="E5">
-        <v>446.1665637789517</v>
+        <v>135.4748664752236</v>
       </c>
       <c r="F5">
-        <v>6.312363483505758E-11</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>65.01894475091952</v>
+        <v>44.13698764335435</v>
       </c>
       <c r="H5">
-        <v>45.26142305921647</v>
+        <v>25.21763127998832</v>
       </c>
       <c r="I5" t="b">
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K5">
-        <v>-1651.283804041921</v>
+        <v>-1475.023977506512</v>
       </c>
       <c r="L5">
-        <v>40000</v>
-      </c>
-      <c r="M5" t="b">
+        <v>0.1382337266527461</v>
+      </c>
+      <c r="M5" t="s">
+        <v>26</v>
+      </c>
+      <c r="N5">
+        <v>50000</v>
+      </c>
+      <c r="O5" t="b">
         <v>0</v>
       </c>
-      <c r="N5">
-        <v>61</v>
-      </c>
-      <c r="O5">
-        <v>116</v>
-      </c>
       <c r="P5">
-        <v>311</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>24</v>
+        <v>256</v>
+      </c>
+      <c r="Q5">
+        <v>140</v>
       </c>
       <c r="R5">
-        <v>-1728.337383867849</v>
-      </c>
-      <c r="S5">
-        <v>602.4965441756756</v>
+        <v>92</v>
+      </c>
+      <c r="S5" t="s">
+        <v>27</v>
+      </c>
+      <c r="T5">
+        <v>-1327.782510114687</v>
+      </c>
+      <c r="U5">
+        <v>260.7535698764785</v>
       </c>
     </row>
   </sheetData>
